--- a/experiment/Omni_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/Omni_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.74</v>
+        <v>33.71</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8938</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.75</v>
+        <v>35.05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9416</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.52</v>
+        <v>28.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.916</v>
+        <v>0.9189000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.92</v>
+        <v>32.93</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7966</v>
+        <v>0.7971</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.56</v>
+        <v>30.63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9106</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.1</v>
+        <v>32.18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8917</v>
+        <v>0.8935</v>
       </c>
     </row>
   </sheetData>
